--- a/docs/Test_Report/Cdd_Sent/TestPlanExecutionReport_Sent.xlsx
+++ b/docs/Test_Report/Cdd_Sent/TestPlanExecutionReport_Sent.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,12 +72,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B050"/>
+        <fgColor rgb="000000FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
+        <fgColor rgb="0000B050"/>
       </patternFill>
     </fill>
     <fill>
@@ -724,7 +724,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624,MCAL-29625</t>
+          <t>MCAL-30800,MCAL-30799</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30 23:35:39.921503-05:00 CDT</t>
+          <t>2025-06-09 06:50:40.874158-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,32 +806,32 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -880,14 +880,14 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -905,7 +905,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1028,32 +1028,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>20%</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
@@ -1409,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1545,32 +1545,32 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29502</t>
+          <t>MCAL-29756</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the MTP mode when PduR integration with comstack disabled</t>
+          <t>CddSent :  Verify CddSent in Mtp mode with external triggers</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28776,MCAL-28681</t>
+          <t>MCAL-28649</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>User Callback function need to read the data when PduR is disabled</t>
+          <t>Verify CddSent in Mtp mode with external triggers</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>User Callback function need to read the data when PduR is disabled</t>
+          <t>Data from the channel should be available for the upper layer</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
@@ -1625,41 +1625,41 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
       <c r="U2" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29501</t>
+          <t>MCAL-29753</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the Standard mode when  PduRintegration with comstack disabled</t>
+          <t>Positive check to verify MTP mode when timestamp nd usercallback is null</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28650</t>
+          <t>MCAL-28659</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1684,17 +1684,18 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>User Callback function need to read the data when PduR is disabled</t>
+          <t xml:space="preserve">Positive check to verify MTP mode when timestampa nd usercallback is null
+ </t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>Manual Verification</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -1724,53 +1725,45 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29233</t>
+          <t>MCAL-29640</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Positive test case to validate the Cdd_Sent_Disable_Interrupts() API and all configuration data is valid</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Architecture</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29237</t>
-        </is>
-      </c>
+          <t>clone Test to check the service provided  PduR_Cdd_Sent_RxIndication to receive the data in Standarad mode</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
@@ -1778,12 +1771,12 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module and hardware should disable the interrupts</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1793,7 +1786,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module and hardware should disable the interrupts</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -1823,51 +1816,51 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29230</t>
+          <t>MCAL-29502</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Cdd_Sent_Enable_Interrupts API Positive Integration Test</t>
+          <t>CddSent : Test case to verify the MTP mode when PduR integration with comstack disabled</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29236</t>
+          <t>MCAL-28776,MCAL-28681</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1877,12 +1870,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Integration test case to verify the functionality of Cdd_Sent_Enable_Interrupts () API which enables the interrupts</t>
+          <t>User Callback function need to read the data when PduR is disabled</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1892,7 +1885,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be de-initialized without any errors.</t>
+          <t>User Callback function need to read the data when PduR is disabled</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -1922,51 +1915,51 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29053</t>
+          <t>MCAL-29501</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Code coverage for slow mode when channel count is 0</t>
+          <t>CddSent : Test case to verify the Standard mode when  PduRintegration with comstack disabled</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28647,MCAL-28650</t>
+          <t>MCAL-28650</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1981,7 +1974,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Code coverage for slow mode when channel count is 0</t>
+          <t>User Callback function need to read the data when PduR is disabled</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1991,7 +1984,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -2011,7 +2004,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -2021,51 +2014,51 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29052</t>
+          <t>MCAL-29233</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Code coverage for slow mode when user callback is null</t>
+          <t>Positive test case to validate the Cdd_Sent_Disable_Interrupts() API and all configuration data is valid</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28650</t>
+          <t>MCAL-29237</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -2075,12 +2068,12 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Code coverage for slow mode when user callback is null</t>
+          <t>CDD_SENT module and hardware should disable the interrupts</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -2090,7 +2083,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>CDD_SENT module and hardware should disable the interrupts</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -2120,51 +2113,51 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28862</t>
+          <t>MCAL-29230</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Performace testcase in Stanadard mode</t>
+          <t>CddSent : Cdd_Sent_Enable_Interrupts API Positive Integration Test</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28650</t>
+          <t>MCAL-29236</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -2174,12 +2167,12 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>|CddSent : Performace testcase in Stanadard Mode mode|</t>
+          <t>Integration test case to verify the functionality of Cdd_Sent_Enable_Interrupts () API which enables the interrupts</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -2189,7 +2182,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>CddSent module and hardware should be de-initialized without any errors.</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
@@ -2219,51 +2212,51 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28861</t>
+          <t>MCAL-29053</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Performance tests to Validate Mtp Mode</t>
+          <t>Code coverage for slow mode when channel count is 0</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28776</t>
+          <t>MCAL-28647,MCAL-28650</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2278,7 +2271,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>|Performance tests to Validate Mtp Mode|</t>
+          <t>Code coverage for slow mode when channel count is 0</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -2308,7 +2301,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -2318,41 +2311,41 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28860</t>
+          <t>MCAL-29052</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Test case to verify the Enhanced 16-bit slow mode in MTP mode</t>
+          <t>Code coverage for slow mode when user callback is null</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -2362,7 +2355,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28752</t>
+          <t>MCAL-28650</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2377,7 +2370,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>|Test case to verify the Enhanced 16-bit slow mode in MTP mode|</t>
+          <t>Code coverage for slow mode when user callback is null</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -2417,51 +2410,51 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U10" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28859</t>
+          <t>MCAL-28862</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the slow mode in MTP mode</t>
+          <t>CddSent : Performace testcase in Stanadard mode</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28752,MCAL-28753</t>
+          <t>MCAL-28650</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -2476,18 +2469,17 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer.
- </t>
+          <t>|CddSent : Performace testcase in Stanadard Mode mode|</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Manual Verification</t>
+          <t>Manual verification</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer.</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
@@ -2517,41 +2509,41 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U11" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28854</t>
+          <t>MCAL-28861</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Sent : Stress Test case to Validate Mtp Mode</t>
+          <t>Performance tests to Validate Mtp Mode</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -2561,7 +2553,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28758</t>
+          <t>MCAL-28776</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -2576,18 +2568,17 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module should send data continuously in Mtp mode</t>
+          <t>|Performance tests to Validate Mtp Mode|</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manual Verification
-</t>
+          <t>Manual verification</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module should send data continuously in Mtp mode</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -2617,41 +2608,41 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28853</t>
+          <t>MCAL-28860</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Cdd_Sent : Stress Test case to Validate stanadard Mode</t>
+          <t>Test case to verify the Enhanced 16-bit slow mode in MTP mode</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2661,7 +2652,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28758</t>
+          <t>MCAL-28752</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -2676,17 +2667,17 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module should send data continuously to upper layers in Standard mode</t>
+          <t>|Test case to verify the Enhanced 16-bit slow mode in MTP mode|</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Manual Verification</t>
+          <t>Manual verification</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module should send data continuously to upper layers in Standard mode</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
@@ -2716,51 +2707,51 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28852</t>
+          <t>MCAL-28859</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Test to cover code coverage issues CodeCoverage when Invalid sensor configured</t>
+          <t>CddSent : Test case to verify the slow mode in MTP mode</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28714</t>
+          <t>MCAL-28752,MCAL-28753</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2775,7 +2766,8 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT module and hardware should be initialized without any errors.</t>
+          <t xml:space="preserve">Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer.
+ </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -2785,7 +2777,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer.</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
@@ -2805,7 +2797,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Full,Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
@@ -2815,51 +2807,51 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28851</t>
+          <t>MCAL-28854</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Test to check the service provided  CddSentUserErrorCallbackFunction in MTP mode</t>
+          <t>Cdd_Sent : Stress Test case to Validate Mtp Mode</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28665,MCAL-28834,MCAL-28622</t>
+          <t>MCAL-28758</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2874,18 +2866,18 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CddSent module and hardware should be initialized without any errors.
- </t>
+          <t>CDD_SENT module should send data continuously in Mtp mode</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Manual Verification</t>
+          <t xml:space="preserve">Manual Verification
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>CDD_SENT module should send data continuously in Mtp mode</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
@@ -2915,41 +2907,41 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28850</t>
+          <t>MCAL-28853</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Test to check the service provided  PduR_Cdd_Sent_RxIndication to receive the data in MTP mode</t>
+          <t>Cdd_Sent : Stress Test case to Validate stanadard Mode</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -2959,7 +2951,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28682</t>
+          <t>MCAL-28758</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2974,17 +2966,17 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
+          <t>CDD_SENT module should send data continuously to upper layers in Standard mode</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>Manual Verification</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>CDD_SENT module should send data continuously to upper layers in Standard mode</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -3014,51 +3006,51 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28849</t>
+          <t>MCAL-28852</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Test to check the service provided  CddSentUserErrorCallbackFunction in Standarad mode</t>
+          <t>Test to cover code coverage issues CodeCoverage when Invalid sensor configured</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28622,MCAL-28834,MCAL-28665</t>
+          <t>MCAL-28714</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -3073,12 +3065,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
+          <t>CDD_SENT module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>Manual Verification</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -3103,7 +3095,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Full,Sanity</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
@@ -3113,51 +3105,51 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28848</t>
+          <t>MCAL-28851</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Test to check the service provided  PduR_Cdd_Sent_RxIndication to receive the data in Standarad mode</t>
+          <t>Test to check the service provided  CddSentUserErrorCallbackFunction in MTP mode</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28682</t>
+          <t>MCAL-28665,MCAL-28834,MCAL-28622</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -3172,12 +3164,13 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
+          <t xml:space="preserve">CddSent module and hardware should be initialized without any errors.
+ </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>Manual verification</t>
+          <t>Manual Verification</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -3212,51 +3205,51 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28844</t>
+          <t>MCAL-28850</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-4 channel</t>
+          <t>Test to check the service provided  PduR_Cdd_Sent_RxIndication to receive the data in MTP mode</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28776,MCAL-28675,MCAL-28723</t>
+          <t>MCAL-28682</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -3311,51 +3304,51 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
       <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U19" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28843</t>
+          <t>MCAL-28849</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-3 channel</t>
+          <t>Test to check the service provided  CddSentUserErrorCallbackFunction in Standarad mode</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28762,MCAL-28723</t>
+          <t>MCAL-28622,MCAL-28834,MCAL-28665</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3410,51 +3403,51 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
       <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U20" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28842</t>
+          <t>MCAL-28848</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-2 channel</t>
+          <t>Test to check the service provided  PduR_Cdd_Sent_RxIndication to receive the data in Standarad mode</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28754,MCAL-28723</t>
+          <t>MCAL-28682</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3509,51 +3502,51 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
       <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U21" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28841</t>
+          <t>MCAL-28844</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-1 channel</t>
+          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-4 channel</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28759,MCAL-28718,MCAL-28837,MCAL-28646,MCAL-28649,MCAL-28757,MCAL-28659,MCAL-28681,MCAL-28635,MCAL-28723,MCAL-28611</t>
+          <t>MCAL-28776,MCAL-28675,MCAL-28723</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -3608,51 +3601,51 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28840</t>
+          <t>MCAL-28843</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and all configuration data is valid</t>
+          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-3 channel</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28745,MCAL-28744,MCAL-28735,MCAL-28740,MCAL-28739</t>
+          <t>MCAL-28762,MCAL-28723</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3662,7 +3655,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -3707,51 +3700,51 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28839</t>
+          <t>MCAL-28842</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>CddSent :  Verify CddSent in MTP mode</t>
+          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-2 channel</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28820,MCAL-28819,MCAL-28824,MCAL-28821,MCAL-28817,MCAL-28818,MCAL-28816,MCAL-28825</t>
+          <t>MCAL-28754,MCAL-28723</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -3761,12 +3754,12 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>|Verify CddSent with MTP sensor|</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -3796,7 +3789,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
@@ -3806,51 +3799,51 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27748</t>
+          <t>MCAL-28841</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the Enhanced 16-bit slow mode.</t>
+          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and input is Sensor-1 channel</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28752</t>
+          <t>MCAL-28759,MCAL-28718,MCAL-28837,MCAL-28646,MCAL-28649,MCAL-28757,MCAL-28659,MCAL-28681,MCAL-28635,MCAL-28723,MCAL-28611</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -3865,7 +3858,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Test case to verify the Enhanced 16-bit slow mode.</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -3875,7 +3868,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3905,51 +3898,51 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
       <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27747</t>
+          <t>MCAL-28840</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the Enhanced 12-bit slow mode.</t>
+          <t>CDD_SENT : Positive test case to validate the Cdd_Sent_Transmit() API and all configuration data is valid</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Architecture,Architecture,Architecture,Architecture,Architecture</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28752,MCAL-28833</t>
+          <t>MCAL-28745,MCAL-28744,MCAL-28735,MCAL-28740,MCAL-28739</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3959,12 +3952,12 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Integration</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Test case to verify the Enhanced 12-bit slow mode.</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3974,7 +3967,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4004,51 +3997,51 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27746</t>
+          <t>MCAL-28839</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 5</t>
+          <t>CddSent :  Verify CddSent in MTP mode</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28638,MCAL-28645</t>
+          <t>MCAL-28820,MCAL-28819,MCAL-28824,MCAL-28821,MCAL-28817,MCAL-28818,MCAL-28816,MCAL-28825</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4058,12 +4051,12 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 5</t>
+          <t>|Verify CddSent with MTP sensor|</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -4103,41 +4096,41 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U27" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27745</t>
+          <t>MCAL-27748</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 4</t>
+          <t>CddSent : Test case to verify the Enhanced 16-bit slow mode.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4147,7 +4140,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28638</t>
+          <t>MCAL-28752</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -4162,7 +4155,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
+          <t>Test case to verify the Enhanced 16-bit slow mode.</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4172,7 +4165,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4202,51 +4195,51 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
       <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U28" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27744</t>
+          <t>MCAL-27747</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 3</t>
+          <t>CddSent : Test case to verify the Enhanced 12-bit slow mode.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28638</t>
+          <t>MCAL-28752,MCAL-28833</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -4261,7 +4254,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 3</t>
+          <t>Test case to verify the Enhanced 12-bit slow mode.</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -4271,7 +4264,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
@@ -4301,51 +4294,51 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
       <c r="T29" s="3" t="inlineStr"/>
-      <c r="U29" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27743</t>
+          <t>MCAL-27746</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 2</t>
+          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 5</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28638</t>
+          <t>MCAL-28638,MCAL-28645</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4360,7 +4353,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 2</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 5</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -4390,7 +4383,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
@@ -4400,51 +4393,51 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U30" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27742</t>
+          <t>MCAL-27745</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 1</t>
+          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 4</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28768,MCAL-28638,MCAL-28755</t>
+          <t>MCAL-28638</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4459,7 +4452,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 1</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -4499,51 +4492,51 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
       <c r="T31" s="3" t="inlineStr"/>
-      <c r="U31" s="11" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="U31" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27528</t>
+          <t>MCAL-27744</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Manual Test To Verify AUTOSAR 4.3.1 Functional requirement</t>
+          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 3</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Design,Requirement</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28683,MCAL-28826</t>
+          <t>MCAL-28638</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4553,12 +4546,12 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Manually verify AUTOSAR 4.3.1 Functional requirement.</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 3</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -4568,7 +4561,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Check if AUTOSAR 4.3.1 Requirements are satisfied</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -4588,7 +4581,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
@@ -4598,51 +4591,51 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="inlineStr"/>
       <c r="U32" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27527</t>
+          <t>MCAL-27743</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Manual Test To verify CddSent Header File inclusions to satisfy AUTOSAR 4.3.1 requirements</t>
+          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 2</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28612,MCAL-28610,MCAL-28683,MCAL-28611,MCAL-28614,MCAL-28623,MCAL-28613</t>
+          <t>MCAL-28638</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4657,7 +4650,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Manually verify all header files required for CddSent driver are included correctly as per Autosar 4.3.1 requirements</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 2</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -4667,7 +4660,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>check if All header files required for CddSent driver are included correctly as per Autosar 4.3.1 requirements</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
@@ -4687,7 +4680,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4697,51 +4690,51 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="inlineStr"/>
       <c r="U33" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27526</t>
+          <t>MCAL-27742</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Testcase to capture ECUC Requirements</t>
+          <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when Nibble count is 1</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design,Design,Design</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28669,MCAL-28670,MCAL-28684,MCAL-28728,MCAL-28731,MCAL-28734,MCAL-28695,MCAL-28732,MCAL-28710,MCAL-28720,MCAL-28713,MCAL-28733,MCAL-28667,MCAL-28724,MCAL-28729,MCAL-28706,MCAL-28715,MCAL-28711,MCAL-28701,MCAL-28694,MCAL-28707,MCAL-28688,MCAL-28704,MCAL-28703,MCAL-28719,MCAL-28721,MCAL-28712,MCAL-28722,MCAL-28700,MCAL-28727,MCAL-28705,MCAL-28691,MCAL-28689,MCAL-28709,MCAL-28697,MCAL-28716,MCAL-28698,MCAL-28696,MCAL-28661,MCAL-28686,MCAL-28717,MCAL-28699,MCAL-28726,MCAL-28690,MCAL-28692,MCAL-28693,MCAL-28708,MCAL-28730,MCAL-28725</t>
+          <t>MCAL-28768,MCAL-28638,MCAL-28755</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4756,7 +4749,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Verify this test case Manually through code review of generated configuration files which holds CddSent driver module config details.</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 1</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -4766,7 +4759,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>Verify this test case Manually through code review of generated configuration files which holds CddSent driver module config details.</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -4786,7 +4779,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Sanity</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
@@ -4796,51 +4789,51 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="inlineStr"/>
       <c r="U34" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27525</t>
+          <t>MCAL-27528</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>CddSent : CddSent reports development errors and runtime/production errors</t>
+          <t>CddSent : Manual Test To Verify AUTOSAR 4.3.1 Functional requirement</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Requirement</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28627,MCAL-28680</t>
+          <t>MCAL-28683,MCAL-28826</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -4850,12 +4843,12 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Qualification</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Verify CddSent reports development errors and runtime/production errors</t>
+          <t>Manually verify AUTOSAR 4.3.1 Functional requirement.</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -4865,7 +4858,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Verify CddSent reports development errors and runtime/production errors . This can be done by code review</t>
+          <t>Check if AUTOSAR 4.3.1 Requirements are satisfied</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -4895,41 +4888,41 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
       <c r="T35" s="3" t="inlineStr"/>
       <c r="U35" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27524</t>
+          <t>MCAL-27527</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>CddSent Module : File Structure</t>
+          <t>CddSent : Manual Test To verify CddSent Header File inclusions to satisfy AUTOSAR 4.3.1 requirements</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4939,7 +4932,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28619,MCAL-28615,MCAL-28620,MCAL-28632,MCAL-29150,MCAL-28616,MCAL-28618</t>
+          <t>MCAL-28612,MCAL-28610,MCAL-28683,MCAL-28611,MCAL-28614,MCAL-28623,MCAL-28613</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -4954,7 +4947,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Verify this test case Manually through code review of files and folder structure which holds CddSent driver module config details and code implementatation and hardware registers information</t>
+          <t>Manually verify all header files required for CddSent driver are included correctly as per Autosar 4.3.1 requirements</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4964,7 +4957,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>Verify this test case Manually through code review of  files and folder structure which holds CddSent driver module config details and code implementatation and hardware registers information</t>
+          <t>check if All header files required for CddSent driver are included correctly as per Autosar 4.3.1 requirements</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -4994,51 +4987,51 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
       <c r="T36" s="3" t="inlineStr"/>
       <c r="U36" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27523</t>
+          <t>MCAL-27526</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test case to verify the slow mode.</t>
+          <t>CddSent : Testcase to capture ECUC Requirements</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28833,MCAL-28752</t>
+          <t>MCAL-28669,MCAL-28670,MCAL-28684,MCAL-28728,MCAL-28731,MCAL-28734,MCAL-28695,MCAL-28732,MCAL-28710,MCAL-28720,MCAL-28713,MCAL-28733,MCAL-28667,MCAL-28724,MCAL-28729,MCAL-28706,MCAL-28715,MCAL-28711,MCAL-28701,MCAL-28694,MCAL-28707,MCAL-28688,MCAL-28704,MCAL-28703,MCAL-28719,MCAL-28721,MCAL-28712,MCAL-28722,MCAL-28700,MCAL-28727,MCAL-28705,MCAL-28691,MCAL-28689,MCAL-28709,MCAL-28697,MCAL-28716,MCAL-28698,MCAL-28696,MCAL-28661,MCAL-28686,MCAL-28717,MCAL-28699,MCAL-28726,MCAL-28690,MCAL-28692,MCAL-28693,MCAL-28708,MCAL-28730,MCAL-28725</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5053,7 +5046,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Test case to verify the slow mode</t>
+          <t>Verify this test case Manually through code review of generated configuration files which holds CddSent driver module config details.</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -5063,7 +5056,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
+          <t>Verify this test case Manually through code review of generated configuration files which holds CddSent driver module config details.</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
@@ -5083,7 +5076,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Sanity</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
@@ -5093,51 +5086,51 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr"/>
       <c r="U37" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27522</t>
+          <t>MCAL-27525</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Check interrupts are generating correctly after receiving data from sensor</t>
+          <t>CddSent : CddSent reports development errors and runtime/production errors</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28664,MCAL-28621,MCAL-28624,MCAL-28671,MCAL-28677</t>
+          <t>MCAL-28627,MCAL-28680</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -5152,7 +5145,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Check interrupts are generating correctly after receiving data from sensor</t>
+          <t>Verify CddSent reports development errors and runtime/production errors</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5162,7 +5155,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>Check interrupts are generating correctly after receiving data from sensor</t>
+          <t>Verify CddSent reports development errors and runtime/production errors . This can be done by code review</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -5182,7 +5175,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Sanity</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
@@ -5192,51 +5185,51 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="inlineStr"/>
       <c r="U38" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27521</t>
+          <t>MCAL-27524</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Test to check the service provided  User Call back notification function  to receive the data</t>
+          <t>CddSent Module : File Structure</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Design,Design</t>
+          <t>Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28648,MCAL-28702</t>
+          <t>MCAL-28619,MCAL-28615,MCAL-28620,MCAL-28632,MCAL-29150,MCAL-28616,MCAL-28618</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -5251,7 +5244,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Test to check the service provided  User call back notifcation  to receive the data</t>
+          <t>Verify this test case Manually through code review of files and folder structure which holds CddSent driver module config details and code implementatation and hardware registers information</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -5261,7 +5254,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>Data from the channel should be available for the upper layer</t>
+          <t>Verify this test case Manually through code review of  files and folder structure which holds CddSent driver module config details and code implementatation and hardware registers information</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5281,7 +5274,7 @@
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Full,Regression</t>
+          <t>Sanity</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
@@ -5291,51 +5284,51 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27510</t>
+          <t>MCAL-27523</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when input pointer is NULL</t>
+          <t>CddSent : Test case to verify the slow mode.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28772,MCAL-28647,MCAL-28679,MCAL-28674,MCAL-28761,MCAL-28771,MCAL-28768,MCAL-29152,MCAL-28633,MCAL-28832,MCAL-28639,MCAL-28838,MCAL-28835,MCAL-28756,MCAL-28764,MCAL-28760,MCAL-28636,MCAL-28773,MCAL-28767,MCAL-28774,MCAL-28666,MCAL-28685,MCAL-28676,MCAL-28668,MCAL-28653,MCAL-28775,MCAL-28640,MCAL-28763,MCAL-28642,MCAL-28650,MCAL-28626,MCAL-28672,MCAL-28831,MCAL-28634,MCAL-28643,MCAL-28687,MCAL-28769,MCAL-28766,MCAL-28836,MCAL-28641,MCAL-28678,MCAL-28770</t>
+          <t>MCAL-28833,MCAL-28752</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -5350,7 +5343,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API which initialises config parameters.</t>
+          <t>Test case to verify the slow mode</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -5360,7 +5353,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Slow channel should be active and slow channel data should be read from Receiver slow channel data register(RSDATA) and the data should be available for the upper layer</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -5390,51 +5383,51 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
       <c r="T40" s="3" t="inlineStr"/>
       <c r="U40" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27508</t>
+          <t>MCAL-27522</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when CRC is     SENT_CRC_RECOMENDED_2010</t>
+          <t>CddSent : Check interrupts are generating correctly after receiving data from sensor</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Design,Design,Design</t>
+          <t>Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28676,MCAL-28637,MCAL-28830</t>
+          <t>MCAL-28664,MCAL-28621,MCAL-28624,MCAL-28671,MCAL-28677</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -5449,7 +5442,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Unit test case to verify the functionality of Cdd_Sent_Init API which CRC is SENT_CRC_RECOMENDED_2010</t>
+          <t>Check interrupts are generating correctly after receiving data from sensor</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -5459,7 +5452,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Check interrupts are generating correctly after receiving data from sensor</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -5489,51 +5482,51 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
       <c r="T41" s="3" t="inlineStr"/>
       <c r="U41" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27506</t>
+          <t>MCAL-27521</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>CddSent : Cdd_Sent_Init API Positive Integration test</t>
+          <t>CddSent : Test to check the service provided  User Call back notification function  to receive the data</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
+          <t>Design,Design</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28828,MCAL-28737,MCAL-28736,MCAL-28741,MCAL-29163,MCAL-28827,MCAL-28738</t>
+          <t>MCAL-28648,MCAL-28702</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -5543,12 +5536,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Integration</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Integration test case to verify the functionality of Cdd_Sent_Init API which initialises config parameters..</t>
+          <t>Test to check the service provided  User call back notifcation  to receive the data</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -5558,7 +5551,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>CddSent module and hardware should be initialized without any errors.</t>
+          <t>Data from the channel should be available for the upper layer</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -5588,51 +5581,51 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
       <c r="T42" s="3" t="inlineStr"/>
       <c r="U42" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29623</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Manual Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-27503</t>
+          <t>MCAL-27510</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CddSent :  Verify CddSent in standard mode</t>
+          <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when input pointer is NULL</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+          <t>Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design,Design</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29036,MCAL-29038,MCAL-29037,MCAL-29042,MCAL-29044,MCAL-29043,MCAL-29040,MCAL-28821,MCAL-28819,MCAL-28818,MCAL-29035,MCAL-29034,MCAL-28817,MCAL-28816,MCAL-29041,MCAL-29039,MCAL-28825,MCAL-28823,MCAL-28822,MCAL-28820</t>
+          <t>MCAL-28772,MCAL-28647,MCAL-28679,MCAL-28674,MCAL-28761,MCAL-28771,MCAL-28768,MCAL-29152,MCAL-28633,MCAL-28832,MCAL-28639,MCAL-28838,MCAL-28835,MCAL-28756,MCAL-28764,MCAL-28760,MCAL-28636,MCAL-28773,MCAL-28767,MCAL-28774,MCAL-28666,MCAL-28685,MCAL-28676,MCAL-28668,MCAL-28653,MCAL-28775,MCAL-28640,MCAL-28763,MCAL-28642,MCAL-28650,MCAL-28626,MCAL-28672,MCAL-28831,MCAL-28634,MCAL-28643,MCAL-28687,MCAL-28769,MCAL-28766,MCAL-28836,MCAL-28641,MCAL-28678,MCAL-28770</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5642,12 +5635,12 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Qualification</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Verify CddSent with standard sensor</t>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API which initialises config parameters.</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5657,7 +5650,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>Data from the channel should be available for the upper layer</t>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
@@ -5677,7 +5670,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Full,Regression</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5687,70 +5680,367 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29624</t>
+          <t>MCAL-30800</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="10" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Not Executed</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-29626</t>
+          <t>MCAL-30798</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
+          <t>MCAL-27508</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when CRC is     SENT_CRC_RECOMENDED_2010</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Design,Design,Design</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-28676,MCAL-28637,MCAL-28830</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Unit test case to verify the functionality of Cdd_Sent_Init API which CRC is SENT_CRC_RECOMENDED_2010</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>Full,Regression</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>CDD SENT</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30800</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30798</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-27506</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>CddSent : Cdd_Sent_Init API Positive Integration test</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-28828,MCAL-28737,MCAL-28736,MCAL-28741,MCAL-29163,MCAL-28827,MCAL-28738</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Integration</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>Integration test case to verify the functionality of Cdd_Sent_Init API which initialises config parameters..</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>CddSent module and hardware should be initialized without any errors.</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>Full,Regression</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>CDD SENT</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30800</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30798</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Manual Tests</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-27503</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>CddSent :  Verify CddSent in standard mode</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement,Requirement</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-29036,MCAL-29038,MCAL-29037,MCAL-29042,MCAL-29044,MCAL-29043,MCAL-29040,MCAL-28821,MCAL-28819,MCAL-28818,MCAL-29035,MCAL-29034,MCAL-28817,MCAL-28816,MCAL-29041,MCAL-29039,MCAL-28825,MCAL-28823,MCAL-28822,MCAL-28820</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>F29H85x-evm</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Qualification</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>Verify CddSent with standard sensor</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Manual verification</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Data from the channel should be available for the upper layer</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Requirements-Analysis</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>CDD SENT</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30800</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Manual Tests Run</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="10" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
           <t>MCAL-29235</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Negative test case to validate the Cdd_Sent_Disable_Interrupts() API when channel is invalid</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>MCAL-29243,MCAL-29151,MCAL-28610,MCAL-29240</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: 
 CDD_SENT_E_PARAM_POINTER</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -5787,102 +6077,102 @@
 }</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: 
 CDD_SENT_E_PARAM_POINTER</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M47" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr">
+      <c r="N47" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P44" s="3" t="inlineStr">
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr"/>
-      <c r="U44" s="10" t="inlineStr">
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>MCAL-29234</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Negative test case to validate the Cdd_Sent_Disable_Interrupts() API when driver not in init state</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>MCAL-29241,MCAL-29242</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: CDD_SENT_E_UNINIT</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -5919,102 +6209,102 @@
 }</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: CDD_SENT_E_UNINIT</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="M48" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr">
+      <c r="N48" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="O48" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P45" s="3" t="inlineStr">
+      <c r="P48" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q45" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr">
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>MCAL-29232</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Negative test case to validate the Cdd_Sent_Enable_Interrupts() API when channel is invalid</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>MCAL-29238</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: 
 CDD_SENT_E_PARAM_POINTER</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6051,102 +6341,102 @@
 }</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Failure should be detected with the following ERROR code: CDD_SENT_E_PARAM_POINTER
 </t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="M49" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N46" s="3" t="inlineStr">
+      <c r="N49" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
+      <c r="O49" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P46" s="3" t="inlineStr">
+      <c r="P49" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="10" t="inlineStr">
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>MCAL-29231</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Negative test case to validate the Cdd_Sent_Enable_Interrupts() API when driver not in init state</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>MCAL-29238,MCAL-29239</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code: CDD_SENT_E_UNINIT</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6183,102 +6473,102 @@
 }</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Failure should be detected with the following ERROR code: CDD_SENT_E_UNINIT
 </t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M47" s="3" t="inlineStr">
+      <c r="M50" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N47" s="3" t="inlineStr">
+      <c r="N50" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
+      <c r="O50" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P47" s="3" t="inlineStr">
+      <c r="P50" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q47" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R47" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S47" s="3" t="inlineStr"/>
-      <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="10" t="inlineStr">
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>MCAL-28847</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when channel is invalid</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>MCAL-28629,MCAL-28652</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6315,101 +6605,101 @@
 }</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M48" s="3" t="inlineStr">
+      <c r="M51" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr">
+      <c r="N51" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P48" s="3" t="inlineStr">
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q48" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R48" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="10" t="inlineStr">
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>MCAL-28846</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>CddSent : Positive testcase to validate the Cdd_Sent_DeInit() API when channel is invalid</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>MCAL-28658,MCAL-28673</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6446,101 +6736,101 @@
 }</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M49" s="3" t="inlineStr">
+      <c r="M52" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N49" s="3" t="inlineStr">
+      <c r="N52" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
+      <c r="O52" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P49" s="3" t="inlineStr">
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q49" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="inlineStr"/>
-      <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="10" t="inlineStr">
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>MCAL-28845</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>CDD_SENT : Negative test to validate the Cdd_Sent_Transmit() API when the  Cdd_Sent module is not intialized.</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>MCAL-28660,MCAL-28628</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Init API when Nibble count is 4</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6577,101 +6867,101 @@
 }</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M50" s="3" t="inlineStr">
+      <c r="M53" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N50" s="3" t="inlineStr">
+      <c r="N53" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P50" s="3" t="inlineStr">
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q50" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="10" t="inlineStr">
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>MCAL-27520</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>CddSent driver code build: SentVersionInfoApi: On</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>MCAL-28654</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>Test to check whether code is building correctly with SentVersionInfoApi is On</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6708,101 +6998,101 @@
 }</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>No Compilation errors should be observed when CDD_SENT_CFG_GET_VERSION_INFO_API Macro should set be  STD_ON</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M51" s="3" t="inlineStr">
+      <c r="M54" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N51" s="3" t="inlineStr">
+      <c r="N54" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O54" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P51" s="3" t="inlineStr">
+      <c r="P54" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q51" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S51" s="3" t="inlineStr"/>
-      <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="10" t="inlineStr">
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>MCAL-27519</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>CddSent driver code build: SentVersionInfoApi: Off</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>MCAL-28654</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>Test to check whether code is building correctly with SentVersionInfoApi is Off</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6839,101 +7129,101 @@
 }</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
         <is>
           <t>No Compilation errors should be observed when CDD_SENT_CFG_GET_VERSION_INFO_API Macro should set be  STD_OFF</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M52" s="3" t="inlineStr">
+      <c r="M55" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N52" s="3" t="inlineStr">
+      <c r="N55" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
+      <c r="O55" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P52" s="3" t="inlineStr">
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q52" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R52" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S52" s="3" t="inlineStr"/>
-      <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="10" t="inlineStr">
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>MCAL-27518</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>CddSent driver code build:  SentDevErrorDetect: On</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>MCAL-28662</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>Test to check whether code is building correctly with SentDevErrorDetect is On</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -6970,101 +7260,101 @@
 }</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
         <is>
           <t>No Compilation errors should be observed when CDD_SENT_CFG_DEV_ERROR_DETECT Macro should set be STD_ON</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M53" s="3" t="inlineStr">
+      <c r="M56" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N53" s="3" t="inlineStr">
+      <c r="N56" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O56" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P53" s="3" t="inlineStr">
+      <c r="P56" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q53" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R53" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S53" s="3" t="inlineStr"/>
-      <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="10" t="inlineStr">
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>MCAL-27517</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>CddSent driver code build:  SentDevErrorDetect: Off</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>MCAL-28662</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>Test to check whether code is building correctly with SentDevErrorDetect is Off</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7101,101 +7391,101 @@
 }</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>No Compilation errors should be observed when CDD_SENT_CFG_DEV_ERROR_DETECT Macro should set be STD_OFF</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M54" s="3" t="inlineStr">
+      <c r="M57" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr">
+      <c r="N57" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
+      <c r="O57" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P54" s="3" t="inlineStr">
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q54" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R54" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S54" s="3" t="inlineStr"/>
-      <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="10" t="inlineStr">
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>MCAL-27516</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>CddSent : Negative test to validate the Cdd_Sent_Deinit() API when the  CddSent module is not intialized.</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>MCAL-28657</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>Negative test to check uninit DET error for Cdd_Sent_Deinit() API.</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7232,102 +7522,102 @@
 }</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code.
 CDD_SENT_E_UNINIT</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>Fault Injection</t>
         </is>
       </c>
-      <c r="M55" s="3" t="inlineStr">
+      <c r="M58" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N55" s="3" t="inlineStr">
+      <c r="N58" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="O58" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P55" s="3" t="inlineStr">
+      <c r="P58" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q55" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S55" s="3" t="inlineStr"/>
-      <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="10" t="inlineStr">
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>MCAL-27515</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>CddSent : Re-init requires a prior De-init</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>MCAL-28656</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>Re-init requires a prior De-init</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7364,101 +7654,101 @@
 }</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="L59" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M56" s="3" t="inlineStr">
+      <c r="M59" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N56" s="3" t="inlineStr">
+      <c r="N59" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
+      <c r="O59" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P56" s="3" t="inlineStr">
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q56" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S56" s="3" t="inlineStr"/>
-      <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="10" t="inlineStr">
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>MCAL-27514</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>CddSent : Positive testcase to validate the Cdd_Sent_Deinit() API and all configuration data is valid</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>MCAL-28657,MCAL-28625,MCAL-28765,MCAL-28656</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Deinit() API which de-initialises config parameters.</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7495,101 +7785,101 @@
 }</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be de-initialized without any errors.</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M57" s="3" t="inlineStr">
+      <c r="M60" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N57" s="3" t="inlineStr">
+      <c r="N60" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="O60" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P57" s="3" t="inlineStr">
+      <c r="P60" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q57" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R57" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S57" s="3" t="inlineStr"/>
-      <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="10" t="inlineStr">
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>MCAL-27513</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>CddSent : Cdd_Sent_Deinit API Positive Integration Test</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>MCAL-28743</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>Integration test case to verify the functionality of Cdd_Sent_Deinit() API which de-initialises config parameters.</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7626,101 +7916,101 @@
 }</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be de-initialized without any errors.</t>
         </is>
       </c>
-      <c r="L58" s="3" t="inlineStr">
+      <c r="L61" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M58" s="3" t="inlineStr">
+      <c r="M61" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr">
+      <c r="N61" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
+      <c r="O61" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P58" s="3" t="inlineStr">
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q58" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="inlineStr"/>
-      <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="10" t="inlineStr">
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>MCAL-27512</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>CddSent : Negative test to validate the Cdd_Sent_Init() API when the CddSent module is already  initialized.</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>MCAL-28631,MCAL-28651</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>Negative test to check Cdd_Sent_Init() API service for initialization called when already  initialized DET error for Cdd_Sent_Init() API.</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7757,102 +8047,102 @@
 }</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code.
 CDD_SENT_E_ALREADY_INITIALIZED</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>Fault Injection</t>
         </is>
       </c>
-      <c r="M59" s="3" t="inlineStr">
+      <c r="M62" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr">
+      <c r="N62" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O62" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P59" s="3" t="inlineStr">
+      <c r="P62" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q59" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr"/>
-      <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="10" t="inlineStr">
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>MCAL-27511</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>CddSent : Negative testcase to validate the Cdd_Sent_Init() API when input pointer is Valid config pointer  and pre compile variant is enabled</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Design</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>MCAL-28653</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>Negative test to check param invalid pointer DET error for Cdd_Sent_Init() API.</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -7889,102 +8179,102 @@
 }</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code.
 CDD_SENT_E_PARAM_POINTER</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr">
         <is>
           <t>Fault Injection</t>
         </is>
       </c>
-      <c r="M60" s="3" t="inlineStr">
+      <c r="M63" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N60" s="3" t="inlineStr">
+      <c r="N63" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
+      <c r="O63" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P60" s="3" t="inlineStr">
+      <c r="P63" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q60" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S60" s="3" t="inlineStr"/>
-      <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="10" t="inlineStr">
+      <c r="Q63" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>MCAL-27509</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>CDD_SENT: Positive testcase to validate the Cdd_Sent_Init() API when CRC is None</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>MCAL-28644,MCAL-28830</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Init API which CRC is None</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -8021,101 +8311,101 @@
 }</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M61" s="3" t="inlineStr">
+      <c r="M64" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr">
+      <c r="N64" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P61" s="3" t="inlineStr">
+      <c r="P64" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="inlineStr"/>
-      <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="10" t="inlineStr">
+      <c r="Q64" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>MCAL-27507</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>CddSent : Positive testcase to validate the Cdd_Sent_Init() API when CRC is     SENT_CRC_LEGACY_2007</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Design,Design</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>MCAL-28637,MCAL-28830</t>
         </is>
       </c>
-      <c r="G62" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>Unit test case to verify the functionality of Cdd_Sent_Init API which CRC is SENT_CRC_LEGACY_2007</t>
         </is>
       </c>
-      <c r="J62" s="3" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -8152,101 +8442,101 @@
 }</t>
         </is>
       </c>
-      <c r="K62" s="3" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
         <is>
           <t>CddSent module and hardware should be initialized without any errors.</t>
         </is>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="L65" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M62" s="3" t="inlineStr">
+      <c r="M65" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr">
+      <c r="N65" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
+      <c r="O65" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P62" s="3" t="inlineStr">
+      <c r="P65" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q62" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="inlineStr"/>
-      <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="10" t="inlineStr">
+      <c r="Q65" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>MCAL-27505</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>CddSent : Negative test to check param NULL pointer DET error for Cdd_Sent_GetVersionInfo() API.</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Design,Design,Design,Design</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>MCAL-28655,MCAL-28630,MCAL-28654,MCAL-28663</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>Negative test to check param NULL pointer DET error for Cdd_Sent_GetVersionInfo() API.</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -8283,102 +8573,102 @@
 }</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
         <is>
           <t>Failure should be detected with the following ERROR code.
 CDD_SENT_E_PARAM_POINTER</t>
         </is>
       </c>
-      <c r="L63" s="3" t="inlineStr">
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>Fault Injection</t>
         </is>
       </c>
-      <c r="M63" s="3" t="inlineStr">
+      <c r="M66" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N63" s="3" t="inlineStr">
+      <c r="N66" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
+      <c r="O66" s="3" t="inlineStr">
         <is>
           <t>Full,Regression</t>
         </is>
       </c>
-      <c r="P63" s="3" t="inlineStr">
+      <c r="P66" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q63" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr"/>
-      <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="10" t="inlineStr">
+      <c r="Q66" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29626</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT- Automated Tests</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30797</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT- Automated Tests</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>MCAL-27504</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>CddSent : Positive integration test to check Cdd_Sent_GetVersionInfo() API functionality.</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>MCAL-28742</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>F29H85x-evm</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Integration</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>Positive integration test to check Cdd_Sent_GetVersionInfo() API functionality.</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>{
   "common_params": {
@@ -8415,56 +8705,56 @@
 }</t>
         </is>
       </c>
-      <c r="K64" s="3" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>API should show the modules version information.</t>
         </is>
       </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="M64" s="3" t="inlineStr">
+      <c r="M67" s="3" t="inlineStr">
         <is>
           <t>Requirements-Analysis</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr">
+      <c r="N67" s="3" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
+      <c r="O67" s="3" t="inlineStr">
         <is>
           <t>Full,Sanity</t>
         </is>
       </c>
-      <c r="P64" s="3" t="inlineStr">
+      <c r="P67" s="3" t="inlineStr">
         <is>
           <t>CDD SENT</t>
         </is>
       </c>
-      <c r="Q64" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-29625</t>
-        </is>
-      </c>
-      <c r="R64" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.00 : CDD_SENT - Automated Tests Run</t>
-        </is>
-      </c>
-      <c r="S64" s="3" t="inlineStr"/>
-      <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="10" t="inlineStr">
+      <c r="Q67" s="3" t="inlineStr">
+        <is>
+          <t>MCAL-30799</t>
+        </is>
+      </c>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>F29H85xMCAL_01.02.01 : CDD_SENT - Automated Tests Run</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="11" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U64"/>
+  <autoFilter ref="A1:U67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8528,12 +8818,12 @@
           <t>Unique Test Plan Key (Map Test Scenario from QMetry)</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8551,12 +8841,12 @@
           <t>Test Plan Summary (Map Test Scenario from QMetry)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8574,12 +8864,12 @@
           <t>Unique Test Case Key</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8597,12 +8887,12 @@
           <t>Test Case Summary</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8625,12 +8915,12 @@
 Unit Tests &lt;-&gt; Design</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8648,12 +8938,12 @@
           <t xml:space="preserve">Provides the Issue ID  </t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8671,12 +8961,12 @@
           <t>This field specifies the test results.  There should be a separate column for each supported platform (e.g., Platform A, Platform B, Platform C, …) and a overall test result based on the test result for each platform.</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8705,7 +8995,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8723,12 +9013,12 @@
           <t>Detailed description of the test and steps required</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8746,12 +9036,12 @@
           <t>Reference to the required test hardware set-up and environment</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8769,12 +9059,12 @@
           <t>A description of the pass and fail criteria for the test case (Map Success Criteria from Qmetry)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8798,7 +9088,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8818,7 +9108,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8839,7 +9129,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8859,7 +9149,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8879,7 +9169,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8900,7 +9190,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8921,7 +9211,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8942,7 +9232,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8963,7 +9253,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -8984,7 +9274,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9005,7 +9295,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9030,7 +9320,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9051,7 +9341,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9071,7 +9361,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9091,7 +9381,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9134,7 +9424,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9157,7 +9447,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9177,7 +9467,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9197,7 +9487,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="E32" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9217,7 +9507,7 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E33" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9262,12 +9552,12 @@
           <t>Software build name/information for which the test results apply. (Map Test Run Key issuetype from Qmetry)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9285,12 +9575,12 @@
           <t>This field provides necessary JIRA Bug ID for any failed test cases.</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E36" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9308,12 +9598,12 @@
           <t>This field provides necessary JIRA Bug Summary for any failed test cases.</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9332,12 +9622,12 @@
 Test Not Executed</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9352,12 +9642,12 @@
 Test Passed</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D39" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E39" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9372,12 +9662,12 @@
 Test Failed</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9392,12 +9682,12 @@
 Test Blocked because of other test case failure, an Open MR from previous Release, feature not implemented yet, feature not supported by hardware</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D41" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E41" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
@@ -9412,12 +9702,12 @@
 Test is currently Work In Progress.</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
